--- a/output/pdf_financials_xlsx/BGI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BGI.UN.xlsx
@@ -431,6 +431,16 @@
   </sheetPr>
   <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/BGI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BGI.UN.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4.253487</v>
+        <v>9.410363</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.315464</v>
+        <v>4.474692</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.167114</v>
+        <v>3.863699</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.821416</v>
+        <v>3.803431</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.647609</v>
+        <v>3.49327</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.136073</v>
+        <v>2.32555</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.133504</v>
+        <v>2.050153</v>
       </c>
     </row>
     <row r="11">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-95.216992</v>
+        <v>-100.373868</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>26.890508</v>
+        <v>24.73128</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13.815092</v>
+        <v>12.118507</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-2.60112</v>
+        <v>-4.583135</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>32.479776</v>
+        <v>30.634115</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-25.697901</v>
+        <v>-26.887378</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>14.302305</v>
+        <v>13.385656</v>
       </c>
     </row>
     <row r="12">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E347" s="5" t="n">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E352" s="5" t="n">

--- a/output/pdf_financials_xlsx/BGI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BGI.UN.xlsx
@@ -3739,25 +3739,25 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>261.391495</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>296.544604</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>138.101064</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>96.31853099999999</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>65.696538</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>68.771672</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>43.6129</v>
       </c>
     </row>
     <row r="116">
@@ -6927,7 +6927,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>261.391495</v>
       </c>
@@ -17486,7 +17490,11 @@
           <t>179,143 Rice Midstream Partners LP, Private Placement 3,077,613</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>3.95e-06</v>
       </c>
